--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127420117</v>
+        <v>114052548</v>
       </c>
       <c r="B2" t="n">
-        <v>105508</v>
+        <v>57825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,53 +686,57 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>100096</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NNO Nygård, Vstm</t>
+          <t>Kranshällarna, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577122</v>
+        <v>577002</v>
       </c>
       <c r="R2" t="n">
-        <v>6622158</v>
+        <v>6622188</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,17 +760,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2023-06-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På mossa i gles tallskog.</t>
+          <t>Den ses långt borta och flyger närmare obspunkt med norr riktning. Tappas bort bakom träd. Trolig hane.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,29 +789,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Åkerberg</t>
+          <t>Samuel Holdar</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Åkerberg, Thommy Åkerberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>PÖN0100 fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127420135</v>
+        <v>127420117</v>
       </c>
       <c r="B3" t="n">
-        <v>105508</v>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,15 +841,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -841,10 +862,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577121</v>
+        <v>577122</v>
       </c>
       <c r="R3" t="n">
-        <v>6622139</v>
+        <v>6622158</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -906,6 +927,121 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127420135</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NNO Nygård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577121</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6622139</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På mossa i gles tallskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg, Thommy Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114052548</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,8 +1057,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420135</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>